--- a/fixtures/sample-supplier-lookup.xlsx
+++ b/fixtures/sample-supplier-lookup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,6 +605,44 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90006</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KIWI SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>09 000 0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>accounts@kiwiservices.example.co.nz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>

--- a/fixtures/sample-supplier-lookup.xlsx
+++ b/fixtures/sample-supplier-lookup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,6 +643,44 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>90007</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AFTER NZ CO</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>03 9000 0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ap@afternz.example.com</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
